--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2850-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2850-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EBEE0CF-75D5-4969-AD37-4022232A983B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A06B62FE-3982-410D-B4CA-90FBF34A33EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{F0871EA8-6FDF-4BFE-A3FE-3ADC19028577}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{48D2941E-8C67-44B3-AB76-31C7ABCC2817}"/>
   </bookViews>
   <sheets>
     <sheet name="2850-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1565,29 +1565,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF64A79-B7DA-4392-AECF-75F2A8A2E84C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE67C3EE-4096-49EF-B883-BB06523163C0}">
   <dimension ref="A1:X37"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1621,7 +1620,7 @@
       <c r="W1" s="31"/>
       <c r="X1" s="23"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1657,7 +1656,7 @@
       <c r="W2" s="33"/>
       <c r="X2" s="34"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1709,7 +1708,7 @@
       </c>
       <c r="X3" s="37"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1777,7 +1776,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>2024</v>
       </c>
@@ -1849,7 +1848,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="40">
         <v>2023</v>
       </c>
@@ -1921,7 +1920,7 @@
         <v>7.76</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>2022</v>
       </c>
@@ -1993,7 +1992,7 @@
         <v>5.29</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="40">
         <v>2021</v>
       </c>
@@ -2065,7 +2064,7 @@
         <v>7.66</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="38">
         <v>2020</v>
       </c>
@@ -2137,7 +2136,7 @@
         <v>5.34</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="40">
         <v>2019</v>
       </c>
@@ -2209,7 +2208,7 @@
         <v>6.14</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="38">
         <v>2018</v>
       </c>
@@ -2281,7 +2280,7 @@
         <v>7.63</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="40">
         <v>2017</v>
       </c>
@@ -2353,7 +2352,7 @@
         <v>6.59</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="38">
         <v>2016</v>
       </c>
@@ -2425,7 +2424,7 @@
         <v>6.04</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="40">
         <v>2015</v>
       </c>
@@ -2497,7 +2496,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="38">
         <v>2014</v>
       </c>
@@ -2569,7 +2568,7 @@
         <v>5.87</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="40">
         <v>2013</v>
       </c>
@@ -2641,7 +2640,7 @@
         <v>4.6500000000000004</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="38">
         <v>2012</v>
       </c>
@@ -2713,7 +2712,7 @@
         <v>6.03</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="40">
         <v>2011</v>
       </c>
@@ -2785,7 +2784,7 @@
         <v>9.91</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="38">
         <v>2010</v>
       </c>
@@ -2857,7 +2856,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="40">
         <v>2009</v>
       </c>
@@ -2929,7 +2928,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="38">
         <v>2008</v>
       </c>
@@ -3001,7 +3000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="42">
         <v>2007</v>
       </c>
@@ -3073,7 +3072,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="44"/>
       <c r="B23" s="45"/>
       <c r="C23" s="19" t="s">
@@ -3101,7 +3100,7 @@
       <c r="W23" s="51"/>
       <c r="X23" s="47"/>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="52">
         <v>2006</v>
       </c>
@@ -3173,7 +3172,7 @@
         <v>9.43</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="54"/>
       <c r="B25" s="55"/>
       <c r="C25" s="21" t="s">
@@ -3201,7 +3200,7 @@
       <c r="W25" s="61"/>
       <c r="X25" s="57"/>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="42">
         <v>2005</v>
       </c>
@@ -3273,7 +3272,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="44"/>
       <c r="B27" s="45"/>
       <c r="C27" s="19" t="s">
@@ -3301,7 +3300,7 @@
       <c r="W27" s="51"/>
       <c r="X27" s="47"/>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="38">
         <v>2004</v>
       </c>
@@ -3373,7 +3372,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="40">
         <v>2003</v>
       </c>
@@ -3445,7 +3444,7 @@
         <v>7.72</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="38">
         <v>2002</v>
       </c>
@@ -3517,7 +3516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="40">
         <v>2001</v>
       </c>
@@ -3589,7 +3588,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="52">
         <v>2000</v>
       </c>
@@ -3661,7 +3660,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="54"/>
       <c r="B33" s="55"/>
       <c r="C33" s="21" t="s">
@@ -3689,7 +3688,7 @@
       <c r="W33" s="61"/>
       <c r="X33" s="57"/>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="40">
         <v>1999</v>
       </c>
@@ -3761,7 +3760,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="38">
         <v>1998</v>
       </c>
@@ -3833,7 +3832,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="40">
         <v>1997</v>
       </c>
@@ -3905,7 +3904,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="38" t="s">
         <v>56</v>
       </c>
